--- a/Time_zone_data/Manual_data.xlsx
+++ b/Time_zone_data/Manual_data.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="69" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="59">
   <si>
     <t>Key</t>
   </si>
@@ -20,12 +20,18 @@
     <t>Value</t>
   </si>
   <si>
-    <t>Slide ID</t>
+    <t>P8K Slide ID</t>
   </si>
   <si>
     <t>test2</t>
   </si>
   <si>
+    <t>P8K not retrival</t>
+  </si>
+  <si>
+    <t>test11</t>
+  </si>
+  <si>
     <t>Slide ID Additional</t>
   </si>
   <si>
@@ -72,6 +78,30 @@
   </si>
   <si>
     <t>rbcpbs</t>
+  </si>
+  <si>
+    <t>Host IP</t>
+  </si>
+  <si>
+    <t>192.168.0.133</t>
+  </si>
+  <si>
+    <t>User name</t>
+  </si>
+  <si>
+    <t>as76usr</t>
+  </si>
+  <si>
+    <t>Password</t>
+  </si>
+  <si>
+    <t>sigtuple123</t>
+  </si>
+  <si>
+    <t>Target storege area</t>
+  </si>
+  <si>
+    <t>/imgarc</t>
   </si>
   <si>
     <t>Cell name</t>
@@ -499,15 +529,15 @@
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="2" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="4" t="s">
+      <c r="A6" s="2" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" s="3" t="s">
         <v>11</v>
       </c>
     </row>
@@ -515,7 +545,7 @@
       <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="4" t="s">
+      <c r="B7" s="5" t="s">
         <v>13</v>
       </c>
     </row>
@@ -541,6 +571,46 @@
       </c>
       <c r="B10" s="4" t="s">
         <v>19</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="B11" s="4" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="4" t="s">
+        <v>22</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>23</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="4" t="s">
+        <v>24</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="4" t="s">
+        <v>26</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>27</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="4" t="s">
+        <v>28</v>
+      </c>
+      <c r="B15" s="4" t="s">
+        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -564,181 +634,181 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="6" t="s">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>21</v>
+        <v>31</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>22</v>
+        <v>32</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
-        <v>23</v>
+        <v>33</v>
       </c>
       <c r="B2" s="6" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C2" s="6" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>26</v>
+        <v>36</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>27</v>
+        <v>37</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>28</v>
+        <v>38</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>30</v>
+        <v>40</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>33</v>
+        <v>43</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
+        <v>44</v>
+      </c>
+      <c r="B7" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="B7" s="6" t="s">
-        <v>24</v>
-      </c>
       <c r="C7" s="4" t="s">
-        <v>35</v>
+        <v>45</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>36</v>
+        <v>46</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>29</v>
+        <v>39</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>37</v>
+        <v>47</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>25</v>
+        <v>35</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
-        <v>38</v>
+        <v>48</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>39</v>
+        <v>49</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>40</v>
+        <v>50</v>
       </c>
       <c r="B11" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C11" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="C11" s="6" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
-        <v>42</v>
+        <v>52</v>
       </c>
       <c r="B12" s="6" t="s">
+        <v>51</v>
+      </c>
+      <c r="C12" s="6" t="s">
         <v>41</v>
-      </c>
-      <c r="C12" s="6" t="s">
-        <v>31</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>43</v>
+        <v>53</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>44</v>
+        <v>54</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="s">
-        <v>47</v>
+        <v>57</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>46</v>
+        <v>56</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="s">
-        <v>48</v>
+        <v>58</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>24</v>
+        <v>34</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>31</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>

--- a/Time_zone_data/Manual_data.xlsx
+++ b/Time_zone_data/Manual_data.xlsx
@@ -12,7 +12,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="79" uniqueCount="59">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="57">
   <si>
     <t>Key</t>
   </si>
@@ -38,52 +38,46 @@
     <t>add</t>
   </si>
   <si>
+    <t>Time zone</t>
+  </si>
+  <si>
+    <t>America/New_York</t>
+  </si>
+  <si>
+    <t>Offset</t>
+  </si>
+  <si>
+    <t>-04:00</t>
+  </si>
+  <si>
+    <t>Time zone slide</t>
+  </si>
+  <si>
+    <t>timezone</t>
+  </si>
+  <si>
+    <t>set time zone</t>
+  </si>
+  <si>
+    <t>(UTC-04:00) America/New_York</t>
+  </si>
+  <si>
+    <t>pbs setting slide id</t>
+  </si>
+  <si>
+    <t>pltpbs</t>
+  </si>
+  <si>
     <t>Slide ID Additional Info</t>
   </si>
   <si>
     <t>check for info</t>
   </si>
   <si>
-    <t>Time zone</t>
-  </si>
-  <si>
-    <t>America/New_York</t>
-  </si>
-  <si>
-    <t>Offset</t>
-  </si>
-  <si>
-    <t>-04:00</t>
-  </si>
-  <si>
-    <t>Time zone slide</t>
-  </si>
-  <si>
-    <t>timezone</t>
-  </si>
-  <si>
-    <t>set time zone</t>
-  </si>
-  <si>
-    <t>(UTC-04:00) America/New_York</t>
-  </si>
-  <si>
-    <t xml:space="preserve">pbs setting slide id </t>
-  </si>
-  <si>
-    <t>pltpbs</t>
-  </si>
-  <si>
-    <t>pbs setting slide id 2</t>
-  </si>
-  <si>
-    <t>rbcpbs</t>
-  </si>
-  <si>
     <t>Host IP</t>
   </si>
   <si>
-    <t>192.168.0.133</t>
+    <t>192.168.0.176</t>
   </si>
   <si>
     <t>User name</t>
@@ -529,15 +523,15 @@
       <c r="A5" s="2" t="s">
         <v>8</v>
       </c>
-      <c r="B5" s="2" t="s">
+      <c r="B5" s="3" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="6">
-      <c r="A6" s="2" t="s">
+      <c r="A6" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B6" s="3" t="s">
+      <c r="B6" s="5" t="s">
         <v>11</v>
       </c>
     </row>
@@ -545,7 +539,7 @@
       <c r="A7" s="4" t="s">
         <v>12</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" s="4" t="s">
         <v>13</v>
       </c>
     </row>
@@ -566,10 +560,10 @@
       </c>
     </row>
     <row r="10">
-      <c r="A10" s="4" t="s">
+      <c r="A10" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="B10" s="4" t="s">
+      <c r="B10" s="2" t="s">
         <v>19</v>
       </c>
     </row>
@@ -603,14 +597,6 @@
       </c>
       <c r="B14" s="4" t="s">
         <v>27</v>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" s="4" t="s">
-        <v>28</v>
-      </c>
-      <c r="B15" s="4" t="s">
-        <v>29</v>
       </c>
     </row>
   </sheetData>
@@ -634,181 +620,181 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="6" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B1" s="6" t="s">
         <v>1</v>
       </c>
       <c r="C1" s="6" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="D1" s="6" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
     </row>
     <row r="2">
       <c r="A2" s="6" t="s">
+        <v>31</v>
+      </c>
+      <c r="B2" s="6" t="s">
+        <v>32</v>
+      </c>
+      <c r="C2" s="6" t="s">
         <v>33</v>
-      </c>
-      <c r="B2" s="6" t="s">
-        <v>34</v>
-      </c>
-      <c r="C2" s="6" t="s">
-        <v>35</v>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="6" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B3" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C3" s="6" t="s">
-        <v>37</v>
+        <v>35</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="6" t="s">
-        <v>38</v>
+        <v>36</v>
       </c>
       <c r="B4" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C4" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="6" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="B5" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C5" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="6" t="s">
-        <v>42</v>
+        <v>40</v>
       </c>
       <c r="B6" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C6" s="6" t="s">
-        <v>43</v>
+        <v>41</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="s">
-        <v>44</v>
+        <v>42</v>
       </c>
       <c r="B7" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C7" s="4" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="B8" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>39</v>
+        <v>37</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="s">
-        <v>47</v>
+        <v>45</v>
       </c>
       <c r="B9" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C9" s="6" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="B10" s="6" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C10" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" s="6" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="B11" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C11" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="6" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="B12" s="6" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C12" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" s="6" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="B13" s="6" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C13" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="B14" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C14" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="s">
-        <v>57</v>
+        <v>55</v>
       </c>
       <c r="B15" s="6" t="s">
-        <v>56</v>
+        <v>54</v>
       </c>
       <c r="C15" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="s">
-        <v>58</v>
+        <v>56</v>
       </c>
       <c r="B16" s="6" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="C16" s="6" t="s">
-        <v>41</v>
+        <v>39</v>
       </c>
     </row>
     <row r="21" ht="15.75" customHeight="1"/>

--- a/Time_zone_data/Manual_data.xlsx
+++ b/Time_zone_data/Manual_data.xlsx
@@ -77,7 +77,7 @@
     <t>Host IP</t>
   </si>
   <si>
-    <t>192.168.0.176</t>
+    <t>192.168.0.126</t>
   </si>
   <si>
     <t>User name</t>

--- a/Time_zone_data/Manual_data.xlsx
+++ b/Time_zone_data/Manual_data.xlsx
@@ -77,7 +77,7 @@
     <t>Host IP</t>
   </si>
   <si>
-    <t>192.168.0.126</t>
+    <t>192.168.0.211</t>
   </si>
   <si>
     <t>User name</t>
